--- a/src/tests/loader/jmmi_valid.xlsx
+++ b/src/tests/loader/jmmi_valid.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="clean_data" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,14 +26,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="13">
   <si>
     <t xml:space="preserve">uuid</t>
   </si>
   <si>
+    <t xml:space="preserve">question1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">consent</t>
   </si>
   <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">new_value</t>
   </si>
   <si>
@@ -53,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">select_one question1</t>
   </si>
 </sst>
 </file>
@@ -62,11 +74,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -82,6 +95,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,8 +144,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -254,13 +284,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -278,15 +319,40 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -305,24 +371,41 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>5</v>
+      <c r="D2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -341,15 +424,31 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>7</v>
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -368,15 +467,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>8</v>
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -413,14 +520,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
